--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-01-2026.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-pl4060-high-performance-board-insulation-2400-x-1200-x-72-5mm</t>
+          <t>£43.59 Pre Sale Price-£45.83</t>
         </is>
       </c>
     </row>
